--- a/data/trans_bre/IP2002-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 2,79</t>
+          <t>-6,85; 2,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 1,21</t>
+          <t>-9,66; 0,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 6,36</t>
+          <t>-2,46; 6,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 5,82</t>
+          <t>-2,74; 5,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,66; 59,67</t>
+          <t>-67,32; 54,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,33; 27,23</t>
+          <t>-77,43; 18,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,27; 324,11</t>
+          <t>-50,26; 400,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-53,39; 330,81</t>
+          <t>-58,1; 345,89</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 4,31</t>
+          <t>-5,06; 3,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 5,64</t>
+          <t>-2,95; 5,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 5,44</t>
+          <t>-2,01; 5,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 7,78</t>
+          <t>-1,92; 7,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 65,59</t>
+          <t>-45,25; 62,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 110,08</t>
+          <t>-34,73; 118,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,37; 132,74</t>
+          <t>-30,44; 145,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 253,6</t>
+          <t>-34,62; 202,66</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 2,71</t>
+          <t>-7,29; 2,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 3,55</t>
+          <t>-6,18; 4,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,51</t>
+          <t>-3,2; 3,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 1,95</t>
+          <t>-7,6; 2,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,05; 57,9</t>
+          <t>-64,71; 55,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 76,04</t>
+          <t>-60,63; 85,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-61,78; 190,52</t>
+          <t>-62,17; 232,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,65; 41,75</t>
+          <t>-72,94; 48,04</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 7,2</t>
+          <t>-1,44; 6,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 0,77</t>
+          <t>-5,61; 0,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 6,35</t>
+          <t>-2,34; 6,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 6,19</t>
+          <t>-1,9; 6,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,97; 247,94</t>
+          <t>-21,94; 230,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,01; 41,82</t>
+          <t>-82,92; 44,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 188,27</t>
+          <t>-35,15; 180,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,81; 285,48</t>
+          <t>-39,59; 325,79</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 2,17</t>
+          <t>-2,69; 2,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,86</t>
+          <t>-3,83; 0,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,61</t>
+          <t>-0,6; 3,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 3,05</t>
+          <t>-1,25; 3,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-30,84; 36,18</t>
+          <t>-32,34; 32,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-45,24; 15,49</t>
+          <t>-46,34; 13,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 94,65</t>
+          <t>-10,23; 87,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 71,79</t>
+          <t>-21,13; 84,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 2,8</t>
+          <t>-6,38; 3,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 0,87</t>
+          <t>-9,03; 1,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 6,7</t>
+          <t>-2,27; 6,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 5,59</t>
+          <t>-2,38; 5,36</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-67,32; 54,47</t>
+          <t>-64,58; 87,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-77,43; 18,05</t>
+          <t>-76,05; 26,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,26; 400,24</t>
+          <t>-47,48; 353,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-58,1; 345,89</t>
+          <t>-54,12; 328,68</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 3,96</t>
+          <t>-4,4; 4,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 5,78</t>
+          <t>-3,02; 5,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 5,48</t>
+          <t>-2,54; 5,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 7,14</t>
+          <t>-1,81; 7,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-45,25; 62,87</t>
+          <t>-41,73; 72,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 118,16</t>
+          <t>-34,73; 106,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 145,73</t>
+          <t>-33,25; 148,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 202,66</t>
+          <t>-28,32; 238,96</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 2,77</t>
+          <t>-7,15; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 4,04</t>
+          <t>-6,56; 3,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 3,65</t>
+          <t>-3,01; 3,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,14</t>
+          <t>-8,25; 1,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,71; 55,1</t>
+          <t>-65,92; 41,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-60,63; 85,44</t>
+          <t>-63,78; 69,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-62,17; 232,86</t>
+          <t>-63,4; 224,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-72,94; 48,04</t>
+          <t>-74,22; 42,87</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,76</t>
+          <t>-0,91; 7,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 0,72</t>
+          <t>-6,33; 0,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 6,43</t>
+          <t>-2,12; 6,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 6,83</t>
+          <t>-1,67; 6,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 230,75</t>
+          <t>-19,76; 249,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-82,92; 44,38</t>
+          <t>-85,92; 34,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 180,92</t>
+          <t>-29,07; 174,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,59; 325,79</t>
+          <t>-36,05; 315,8</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,01</t>
+          <t>-2,35; 2,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,73</t>
+          <t>-3,52; 0,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,49</t>
+          <t>-0,75; 3,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,24</t>
+          <t>-1,33; 2,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 32,61</t>
+          <t>-28,22; 37,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 13,19</t>
+          <t>-43,91; 14,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 87,79</t>
+          <t>-14,0; 85,88</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 84,68</t>
+          <t>-21,94; 72,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,46</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 3,35</t>
+          <t>-6,71; 2,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 1,13</t>
+          <t>-9,14; 1,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 6,68</t>
+          <t>-2,69; 6,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,36</t>
+          <t>-2,34; 6,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-64,58; 87,92</t>
+          <t>-67,66; 59,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,05; 26,34</t>
+          <t>-76,33; 27,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-47,48; 353,21</t>
+          <t>-51,27; 324,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-54,12; 328,68</t>
+          <t>-51,87; 339,49</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>1,97</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 4,48</t>
+          <t>-4,57; 4,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 5,24</t>
+          <t>-3,23; 5,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 5,67</t>
+          <t>-2,73; 5,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 7,49</t>
+          <t>-1,76; 6,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,73; 72,26</t>
+          <t>-43,27; 65,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-34,73; 106,19</t>
+          <t>-36,41; 110,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,25; 148,58</t>
+          <t>-38,37; 132,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 238,96</t>
+          <t>-31,66; 216,47</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,44</t>
+          <t>-1,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-33,78%</t>
+          <t>-17,66%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 2,4</t>
+          <t>-7,2; 2,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 3,49</t>
+          <t>-6,16; 3,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,78</t>
+          <t>-3,14; 3,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 1,94</t>
+          <t>-6,76; 3,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-65,92; 41,23</t>
+          <t>-63,05; 57,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-63,78; 69,61</t>
+          <t>-59,36; 76,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 224,37</t>
+          <t>-61,78; 190,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,22; 42,87</t>
+          <t>-64,74; 67,51</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,26</t>
+          <t>2,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 7,36</t>
+          <t>-0,61; 7,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 0,52</t>
+          <t>-6,0; 0,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 6,42</t>
+          <t>-2,13; 6,35</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 6,95</t>
+          <t>-1,5; 6,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,76; 249,78</t>
+          <t>-13,97; 247,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,92; 34,16</t>
+          <t>-84,01; 41,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 174,51</t>
+          <t>-29,92; 188,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 315,8</t>
+          <t>-39,83; 300,32</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,9</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>23,92%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 2,21</t>
+          <t>-2,56; 2,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,83</t>
+          <t>-3,73; 0,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,43</t>
+          <t>-0,67; 3,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,95</t>
+          <t>-1,29; 3,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 37,15</t>
+          <t>-30,84; 36,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,91; 14,26</t>
+          <t>-45,24; 15,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 85,88</t>
+          <t>-12,57; 94,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,94; 72,81</t>
+          <t>-20,55; 81,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,07</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-3,95</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,63</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,46</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-26,57%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-44,09%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>42,33%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42,99%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.07466405196769</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-3.946293312806345</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.632685162104134</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>1.46283217258568</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.265748511048818</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.440855895106935</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.4233294706505186</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.4298964787094772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,71; 2,79</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-9,14; 1,21</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,69; 6,36</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,34; 6,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-67,66; 59,67</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-76,33; 27,23</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-51,27; 324,11</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-51,87; 339,49</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.70945255301804</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-9.144518167887899</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.686622311916451</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.337250225171557</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.676583978072093</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.7633057018612128</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.512748277268823</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.5186962988324898</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.787243501465326</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.21079249126978</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.361406249785791</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>6.003606305528693</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.5966585332313132</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2723039659250607</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3.241083486514706</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>3.394859359834212</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,43</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,29</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,97</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-4,98%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>18,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>24,76%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-4,57; 4,31</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-3,23; 5,64</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,73; 5,44</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,76; 6,44</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-43,27; 65,59</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-36,41; 110,08</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-38,37; 132,74</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-31,66; 216,47</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.4326733436784358</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.292669612960733</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.425891220934418</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.970950195594706</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.04983177057268189</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1828088382858499</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2476388246302046</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.3915958710957724</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,24</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-27,03%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-15,31%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,4%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-17,66%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-4.568555679360794</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-3.227782970050586</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.726662675348758</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.759449825944903</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4327402040195614</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3641020383631602</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3837487876571297</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.316605775141514</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 2,71</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,16; 3,55</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,14; 3,51</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-6,76; 3,05</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-63,05; 57,9</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-59,36; 76,04</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-61,78; 190,52</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-64,74; 67,51</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>4.309498230899348</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.636695973310696</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.436793512682951</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>6.442275340297961</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.6558514741305154</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.100803277265256</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.327353574091646</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>2.164745734712573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,87</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-2,38</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,59</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>60,62%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-49,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>67,9%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.243940465365393</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.162672512942232</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.3299979537913209</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-1.274675550489627</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.2703491410296435</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.1530521841530507</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.09402575022373606</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.1766002611157492</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,61; 7,2</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-6,0; 0,77</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,13; 6,35</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,5; 6,54</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-13,97; 247,94</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-84,01; 41,82</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-29,92; 188,27</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-39,83; 300,32</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-7.198354220818412</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.164476934246189</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.13984015111374</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-6.762231221010671</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6305346201865958</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5936135527326527</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6178427560892058</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.6473749902226789</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.707955739929501</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.548693986063025</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.510151157905756</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>3.046856722009086</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.5789523910621696</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.7603837549107403</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.905154321113834</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.6751266997040345</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.871703074337992</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-2.378106430619094</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.978615762086616</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>2.585322794002382</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.6061730003315847</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.4957716950661624</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.3562638028573327</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.6789783176491414</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.6141991135546686</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-6.003939335584393</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.129602741598537</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.496939996637057</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1396707081987423</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.8400732688928496</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2991863664202776</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3983146457462934</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.196066843607435</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.7654371112663634</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.346884511232422</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>6.540561523734624</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.479428551102837</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.418233517053951</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>1.882676958047169</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>3.00319469454073</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,4</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,44%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-20,15%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>29,16%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-2,56; 2,17</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,73; 0,86</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,67; 3,61</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,29; 3,28</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-30,84; 36,18</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-45,24; 15,49</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-12,57; 94,65</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-20,55; 81,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.1777268367883514</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-1.395986701484052</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.402504110776862</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>1.19017431274183</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.02440856104867754</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.2014960809089524</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.2915529311512513</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.2391806891001438</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-2.561496213520331</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.728112116182426</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.6731146281087408</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.286474596661024</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3083854576222361</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.452389747844769</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.125654092743635</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2055199388439939</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>2.172586648884698</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.8633540679179137</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.61371364061364</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.281693127734554</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.3618426206181263</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1548699664372181</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.9465367714625371</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.8138331365737015</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
